--- a/food/hi-kshetriya-pakshailiyan_HI.xlsx
+++ b/food/hi-kshetriya-pakshailiyan_HI.xlsx
@@ -11,240 +11,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>नाम</t>
   </si>
   <si>
-    <t>अंग्रेज़ी नाम</t>
-  </si>
-  <si>
-    <t>स्रोत का अंग्रेज़ी विवरण</t>
-  </si>
-  <si>
-    <t>वर्गीकरण</t>
-  </si>
-  <si>
-    <t>संबंधित संस्कृति</t>
+    <t>स्रोत में दिए व्यंजन</t>
   </si>
   <si>
     <t>स्रोत लिंक</t>
   </si>
   <si>
-    <t>असमिया पाकशैली</t>
-  </si>
-  <si>
-    <t>Assamese cuisine</t>
-  </si>
-  <si>
-    <t>northeast Indian cuisine</t>
-  </si>
-  <si>
-    <t>भारतीय क्षेत्रीय पाकशैली; भारतीय खाना</t>
-  </si>
-  <si>
-    <t>असमिया संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q3595895</t>
-  </si>
-  <si>
-    <t>अवधी पाकशैली</t>
-  </si>
-  <si>
-    <t>Awadhi cuisine</t>
-  </si>
-  <si>
-    <t>culinary traditions of Awadh</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q41928</t>
-  </si>
-  <si>
-    <t>बंगाली पाकशैली</t>
-  </si>
-  <si>
-    <t>Bengali cuisine</t>
-  </si>
-  <si>
-    <t>cuisine from the region of Bengal</t>
-  </si>
-  <si>
-    <t>क्षेत्रीय पाकशैली; दक्षिण एशियाई व्यंजन</t>
-  </si>
-  <si>
-    <t>बंगाल की संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q1572982</t>
-  </si>
-  <si>
-    <t>भोजपुरी पाकशैली</t>
-  </si>
-  <si>
-    <t>Bhojpuri cuisine</t>
-  </si>
-  <si>
-    <t>culinary traditions of Bhojpur region of India</t>
-  </si>
-  <si>
-    <t>समुदाय की पाकशैली; भारतीय-आर्य पाकशैली</t>
-  </si>
-  <si>
-    <t>भोजपुरी संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q4901911</t>
-  </si>
-  <si>
-    <t>बिहारी पाकशैली</t>
-  </si>
-  <si>
-    <t>Bihari cuisine</t>
-  </si>
-  <si>
-    <t>culinary tradition</t>
-  </si>
-  <si>
-    <t>बिहार की संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q42015</t>
-  </si>
-  <si>
-    <t>गोवा की पाकशैली</t>
-  </si>
-  <si>
-    <t>Goan cuisine</t>
-  </si>
-  <si>
-    <t>cuisine from Goa, India, influenced by Portuguese colonial rule</t>
-  </si>
-  <si>
-    <t>गोवा की संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q2025907</t>
-  </si>
-  <si>
-    <t>गुजराती पाकशैली</t>
-  </si>
-  <si>
-    <t>Gujarati cuisine</t>
-  </si>
-  <si>
-    <t>cuisine of Gujarat, India</t>
-  </si>
-  <si>
-    <t>गुजरात की संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q2732159</t>
-  </si>
-  <si>
-    <t>कर्नाटक की पाकशैली</t>
-  </si>
-  <si>
-    <t>Karnataka cuisine</t>
-  </si>
-  <si>
-    <t>cuisine from the state of Karnataka</t>
-  </si>
-  <si>
-    <t>कर्नाटक की संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q5192776</t>
-  </si>
-  <si>
-    <t>कश्मीरी पाकशैली</t>
-  </si>
-  <si>
-    <t>Kashmiri cuisine</t>
-  </si>
-  <si>
-    <t>traditional food dishes from India's Kashmir Valley</t>
-  </si>
-  <si>
-    <t>क्षेत्रीय पाकशैली; एशियाई भोजन</t>
-  </si>
-  <si>
-    <t>कश्मीर की संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q2152857</t>
-  </si>
-  <si>
-    <t>महाराष्ट्रीय पाकशैली</t>
-  </si>
-  <si>
-    <t>Maharashtrian cuisine</t>
-  </si>
-  <si>
-    <t>cuisine of the Marathi people from the state of Maharashtra in India</t>
-  </si>
-  <si>
-    <t>समुदाय की पाकशैली; क्षेत्रीय पाकशैली; भारतीय खाना; भारतीय-आर्य पाकशैली</t>
-  </si>
-  <si>
-    <t>महाराष्ट्र की संस्कृति; भारतीय-आर्य संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q7601803</t>
-  </si>
-  <si>
-    <t>पंजाबी पाकशैली</t>
-  </si>
-  <si>
-    <t>Punjabi cuisine</t>
-  </si>
-  <si>
-    <t>food from the Punjab region of India and Pakistan</t>
-  </si>
-  <si>
-    <t>क्षेत्रीय पाकशैली; समुदाय की पाकशैली; दक्षिण एशियाई व्यंजन; भारतीय-आर्य पाकशैली</t>
-  </si>
-  <si>
-    <t>पंजाबी संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q2090705</t>
-  </si>
-  <si>
-    <t>राजस्थानी पाकशैली</t>
-  </si>
-  <si>
-    <t>Rajasthani cuisine</t>
-  </si>
-  <si>
-    <t>marwadi, mewadi and barmeri cuisine</t>
-  </si>
-  <si>
-    <t>राजस्थान की संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q3595467</t>
-  </si>
-  <si>
-    <t>तमिल पाकशैली</t>
-  </si>
-  <si>
-    <t>Tamil cuisine</t>
-  </si>
-  <si>
-    <t>tamilian cuisine</t>
-  </si>
-  <si>
-    <t>समुदाय की पाकशैली; मानव पाकशैली</t>
-  </si>
-  <si>
-    <t>तमिल संस्कृति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q3007006</t>
+    <t>कश्मीरी</t>
+  </si>
+  <si>
+    <t>यखनी; कश्मीरी पुलाव; गुश्तावा</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%95%E0%A4%B6%E0%A5%8D%E0%A4%AE%E0%A5%80%E0%A4%B0%E0%A5%80</t>
+  </si>
+  <si>
+    <t>डोगरी</t>
+  </si>
+  <si>
+    <t>राजमा चावल; काशीफल का अम्बल; दाल मद्धरा; रौंगी मद्धरा; औहरिया आलू; टिम्बरू चटनी; कलाड़ी कुल्चा; सरियाँ का साग; रेढ़ू ढोडा; खमीरे-भट्ठोरू; कत्तरैड़ आसरा; कसरोड़; गुच्छी पुलाव; घ्यूर; गुलरा; पत्त्रोड़ू</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%A1%E0%A5%8B%E0%A4%97%E0%A4%B0%E0%A5%80</t>
+  </si>
+  <si>
+    <t>पंजाबी</t>
+  </si>
+  <si>
+    <t>तंदूरी चिकन; सरसों का साग; मक्खदाल नी; छोले भटूरे</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%AA%E0%A4%82%E0%A4%9C%E0%A4%BE%E0%A4%AC%E0%A5%80</t>
+  </si>
+  <si>
+    <t>अवधी खाना</t>
+  </si>
+  <si>
+    <t>दम पुख्त; बिरयानी; काकोरी कबाब; शामी कबाब; मलाई गिलौरी</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%85%E0%A4%B5%E0%A4%A7%E0%A5%80_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE</t>
+  </si>
+  <si>
+    <t>राजस्थानी</t>
+  </si>
+  <si>
+    <t>दाल बाटी; चूरमा; लापसी; घेवर; कैर की सब्जी; कड़ी; मावा कचौरी; गट्टे की सब्जी; हल्दी की सब्जी; मंगोड़ी और पिथोड़ी की सब्जी; मूंग दाल, आटे और सिंगोड़े का हलवा; गुंद के लड्डू; पंचमेल सब्जी; सांगरी की सब्जी; कुमटिया की सब्जी</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B8%E0%A5%8D%E0%A4%A5%E0%A4%BE%E0%A4%A8%E0%A5%80</t>
+  </si>
+  <si>
+    <t>गुजराती</t>
+  </si>
+  <si>
+    <t>ढोकला; खांडवी; लापसी; बाफला; थेपला; भाखरी; श्रीखण्ड; खमण; उधिया; फाफडा; गोटा</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%97%E0%A5%81%E0%A4%9C%E0%A4%B0%E0%A4%BE%E0%A4%A4%E0%A5%80</t>
+  </si>
+  <si>
+    <t>महाराष्ट्री</t>
+  </si>
+  <si>
+    <t>वड़ा पाव; श्रीखंड; भेलपूरी; पुरण पोळी; झुणका भाकर; गुर्जर वाल भाजी; गुर्जरोयनी वरण बट्टी; गुर्जरी सफेद कढ़ी; गुर्जरी वाल ना दाना अनं वांगु; गुर्जरी तोर ना दाना अनं वांगु; गुर्जरी वांगा नी घोटेल भाजी; गुर्जरी सग्गा वांगा; गुर्जरी पातोडे नी भाजी; गुर्जर दराबा ना लाडू</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%80</t>
+  </si>
+  <si>
+    <t>कोंकणी/गोआनी</t>
+  </si>
+  <si>
+    <t>धनसाक; विंडालू</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%95%E0%A5%8B%E0%A4%82%E0%A4%95%E0%A4%A3%E0%A5%80/%E0%A4%97%E0%A5%8B%E0%A4%86%E0%A4%A8%E0%A5%80</t>
+  </si>
+  <si>
+    <t>केरल</t>
+  </si>
+  <si>
+    <t>अप्पम; अवियल; फिश मोली</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%95%E0%A5%87%E0%A4%B0%E0%A4%B2</t>
+  </si>
+  <si>
+    <t>दक्षिण भारतीय</t>
+  </si>
+  <si>
+    <t>इडली; सांभर; मैसूर पाक</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%A6%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%BF%E0%A4%A3_%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF</t>
+  </si>
+  <si>
+    <t>हैदराबादी</t>
+  </si>
+  <si>
+    <t>हैदराबादी बिरयानी; हलीम; दाल गोश्त</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%B9%E0%A5%88%E0%A4%A6%E0%A4%B0%E0%A4%BE%E0%A4%AC%E0%A4%BE%E0%A4%A6%E0%A5%80</t>
+  </si>
+  <si>
+    <t>पूर्वी</t>
+  </si>
+  <si>
+    <t>भाप्पा इलिश; माछ झोल; रॉसोगुल्ला; संदेश (मिठाई)</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A5%80</t>
+  </si>
+  <si>
+    <t>पूर्वोत्तर</t>
+  </si>
+  <si>
+    <t>मोमो; थुपका; फिश टेंगा</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/wiki/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%BE#%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A5%8B%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0</t>
   </si>
 </sst>
 </file>
@@ -289,10 +181,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,18 +528,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,278 +546,152 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F7" t="s">
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="14" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" t="s">
-        <v>77</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
